--- a/Excel/PlayerModel.xlsx
+++ b/Excel/PlayerModel.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="生成配置" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="65">
   <si>
     <t>ID</t>
   </si>
@@ -860,7 +860,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -868,13 +868,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1203,7 +1202,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q74"/>
+  <dimension ref="A1:Q80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1377,7 +1376,7 @@
       <c r="C6" s="3">
         <v>1</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="3">
@@ -1406,7 +1405,7 @@
       <c r="C7" s="3">
         <v>2</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="3">
@@ -1420,7 +1419,7 @@
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="8" t="s">
         <v>18</v>
       </c>
       <c r="K7" s="3">
@@ -1435,7 +1434,7 @@
       <c r="C8" s="3">
         <v>3</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E8" s="3">
@@ -1464,7 +1463,7 @@
       <c r="C9" s="3">
         <v>4</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="3">
@@ -1493,7 +1492,7 @@
       <c r="C10" s="3">
         <v>5</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="3" t="s">
         <v>21</v>
       </c>
       <c r="E10" s="3">
@@ -1522,7 +1521,7 @@
       <c r="C11" s="3">
         <v>6</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="3">
@@ -1551,7 +1550,7 @@
       <c r="C12" s="3">
         <v>7</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="E12" s="3">
@@ -1580,7 +1579,7 @@
       <c r="C13" s="3">
         <v>8</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E13" s="3">
@@ -1609,7 +1608,7 @@
       <c r="C14" s="3">
         <v>9</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
@@ -1638,7 +1637,7 @@
       <c r="C15" s="3">
         <v>10</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="3">
@@ -1667,7 +1666,7 @@
       <c r="C16" s="3">
         <v>11</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E16" s="3">
@@ -1696,7 +1695,7 @@
       <c r="C17" s="3">
         <v>12</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="3">
@@ -1710,7 +1709,7 @@
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="8" t="s">
         <v>29</v>
       </c>
       <c r="K17" s="3">
@@ -1725,7 +1724,7 @@
       <c r="C18" s="3">
         <v>13</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E18" s="3">
@@ -1739,7 +1738,7 @@
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="10" t="s">
+      <c r="J18" s="9" t="s">
         <v>31</v>
       </c>
       <c r="K18" s="3">
@@ -1754,7 +1753,7 @@
       <c r="C19" s="3">
         <v>14</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E19" s="3">
@@ -1775,7 +1774,7 @@
       <c r="L19" s="3">
         <v>0</v>
       </c>
-      <c r="M19" s="5" t="s">
+      <c r="M19" s="3" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1796,7 +1795,7 @@
       <c r="C21" s="3">
         <v>3001</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E21" s="3">
@@ -1825,7 +1824,7 @@
       <c r="C22" s="3">
         <v>3002</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E22" s="3">
@@ -1854,7 +1853,7 @@
       <c r="C23" s="3">
         <v>3003</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E23" s="3">
@@ -1883,7 +1882,7 @@
       <c r="C24" s="3">
         <v>3004</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E24" s="3">
@@ -1912,7 +1911,7 @@
       <c r="C25" s="3">
         <v>3005</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E25" s="3">
@@ -1941,7 +1940,7 @@
       <c r="C26" s="3">
         <v>3006</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E26" s="3">
@@ -1955,7 +1954,7 @@
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-      <c r="J26" s="9" t="s">
+      <c r="J26" s="8" t="s">
         <v>35</v>
       </c>
       <c r="K26" s="3">
@@ -1970,7 +1969,7 @@
       <c r="C27" s="3">
         <v>3007</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E27" s="3">
@@ -1984,7 +1983,7 @@
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="9" t="s">
+      <c r="J27" s="8" t="s">
         <v>36</v>
       </c>
       <c r="K27" s="3">
@@ -1999,7 +1998,7 @@
       <c r="C28" s="3">
         <v>3008</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E28" s="3">
@@ -2013,7 +2012,7 @@
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-      <c r="J28" s="9" t="s">
+      <c r="J28" s="8" t="s">
         <v>37</v>
       </c>
       <c r="K28" s="3">
@@ -2028,7 +2027,7 @@
       <c r="C29" s="3">
         <v>3009</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E29" s="3">
@@ -2042,7 +2041,7 @@
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
-      <c r="J29" s="9" t="s">
+      <c r="J29" s="8" t="s">
         <v>38</v>
       </c>
       <c r="K29" s="3">
@@ -2057,7 +2056,7 @@
       <c r="C30" s="3">
         <v>3010</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E30" s="3">
@@ -2071,7 +2070,7 @@
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
-      <c r="J30" s="9" t="s">
+      <c r="J30" s="8" t="s">
         <v>39</v>
       </c>
       <c r="K30" s="3">
@@ -2086,7 +2085,7 @@
       <c r="C31" s="3">
         <v>3011</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E31" s="3">
@@ -2100,7 +2099,7 @@
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
-      <c r="J31" s="9" t="s">
+      <c r="J31" s="8" t="s">
         <v>40</v>
       </c>
       <c r="K31" s="3">
@@ -2115,7 +2114,7 @@
       <c r="C32" s="3">
         <v>3012</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E32" s="3">
@@ -2129,7 +2128,7 @@
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="9" t="s">
+      <c r="J32" s="8" t="s">
         <v>41</v>
       </c>
       <c r="K32" s="3">
@@ -2144,7 +2143,7 @@
       <c r="C33" s="3">
         <v>3013</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E33" s="3">
@@ -2158,7 +2157,7 @@
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
-      <c r="J33" s="9" t="s">
+      <c r="J33" s="8" t="s">
         <v>42</v>
       </c>
       <c r="K33" s="3">
@@ -2173,7 +2172,7 @@
       <c r="C34" s="3">
         <v>3014</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E34" s="3">
@@ -2187,7 +2186,7 @@
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="11" t="s">
+      <c r="J34" s="10" t="s">
         <v>43</v>
       </c>
       <c r="K34" s="3">
@@ -2202,7 +2201,7 @@
       <c r="C35" s="3">
         <v>3015</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E35" s="3">
@@ -2216,7 +2215,7 @@
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
-      <c r="J35" s="9" t="s">
+      <c r="J35" s="8" t="s">
         <v>44</v>
       </c>
       <c r="K35" s="3">
@@ -2231,13 +2230,13 @@
       <c r="C36" s="3">
         <v>3016</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E36" s="3">
         <v>1085</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="5">
         <v>1104</v>
       </c>
       <c r="G36" s="3">
@@ -2245,7 +2244,7 @@
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
-      <c r="J36" s="9" t="s">
+      <c r="J36" s="8" t="s">
         <v>45</v>
       </c>
       <c r="K36" s="3">
@@ -2260,13 +2259,13 @@
       <c r="C37" s="3">
         <v>3017</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E37" s="3">
         <v>1085</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F37" s="5">
         <v>1104</v>
       </c>
       <c r="G37" s="3">
@@ -2274,7 +2273,7 @@
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
-      <c r="J37" s="9" t="s">
+      <c r="J37" s="8" t="s">
         <v>46</v>
       </c>
       <c r="K37" s="3">
@@ -2289,10 +2288,10 @@
       <c r="C38" s="3">
         <v>3018</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="5">
         <v>1105</v>
       </c>
       <c r="F38" s="3">
@@ -2303,7 +2302,7 @@
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
-      <c r="J38" s="9" t="s">
+      <c r="J38" s="8" t="s">
         <v>48</v>
       </c>
       <c r="K38" s="3">
@@ -2318,10 +2317,10 @@
       <c r="C39" s="3">
         <v>3019</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="5">
         <v>1105</v>
       </c>
       <c r="F39" s="3">
@@ -2332,7 +2331,7 @@
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
-      <c r="J39" s="9" t="s">
+      <c r="J39" s="8" t="s">
         <v>49</v>
       </c>
       <c r="K39" s="3">
@@ -2347,10 +2346,10 @@
       <c r="C40" s="3">
         <v>3020</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E40" s="6">
+      <c r="E40" s="5">
         <v>1105</v>
       </c>
       <c r="F40" s="3">
@@ -2361,7 +2360,7 @@
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-      <c r="J40" s="9" t="s">
+      <c r="J40" s="8" t="s">
         <v>50</v>
       </c>
       <c r="K40" s="3">
@@ -2373,138 +2372,138 @@
       <c r="M40" s="3"/>
     </row>
     <row r="41" ht="24" customHeight="1" spans="3:13">
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
+      <c r="C41" s="3">
+        <v>3021</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E41" s="5">
+        <v>1140</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1175</v>
+      </c>
+      <c r="G41" s="3">
+        <v>5</v>
+      </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
+      <c r="J41" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="K41" s="3">
+        <v>10</v>
+      </c>
+      <c r="L41" s="3">
+        <v>10</v>
+      </c>
       <c r="M41" s="3"/>
     </row>
     <row r="42" ht="24" customHeight="1" spans="3:13">
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
+      <c r="C42" s="3">
+        <v>3022</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E42" s="5">
+        <v>1140</v>
+      </c>
+      <c r="F42" s="3">
+        <v>1175</v>
+      </c>
+      <c r="G42" s="3">
+        <v>5</v>
+      </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3"/>
+      <c r="J42" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="K42" s="3">
+        <v>10</v>
+      </c>
+      <c r="L42" s="3">
+        <v>10</v>
+      </c>
       <c r="M42" s="3"/>
     </row>
     <row r="43" ht="24" customHeight="1" spans="3:13">
       <c r="C43" s="3">
-        <v>3101</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E43" s="3">
-        <v>1070</v>
+        <v>3023</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E43" s="5">
+        <v>1140</v>
       </c>
       <c r="F43" s="3">
-        <v>1084</v>
+        <v>1175</v>
       </c>
       <c r="G43" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
-      <c r="J43" s="9" t="s">
-        <v>52</v>
+      <c r="J43" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="K43" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L43" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M43" s="3"/>
     </row>
     <row r="44" ht="24" customHeight="1" spans="3:13">
-      <c r="C44" s="3">
-        <v>3102</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E44" s="3">
-        <v>1070</v>
-      </c>
-      <c r="F44" s="3">
-        <v>1084</v>
-      </c>
-      <c r="G44" s="3">
-        <v>4</v>
-      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
-      <c r="J44" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="K44" s="3">
-        <v>3</v>
-      </c>
-      <c r="L44" s="3">
-        <v>1</v>
-      </c>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
       <c r="M44" s="3"/>
     </row>
     <row r="45" ht="24" customHeight="1" spans="3:13">
-      <c r="C45" s="3">
-        <v>3103</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1070</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1084</v>
-      </c>
-      <c r="G45" s="3">
-        <v>4</v>
-      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
-      <c r="J45" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K45" s="3">
-        <v>3</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1</v>
-      </c>
+      <c r="J45" s="3"/>
+      <c r="K45" s="3"/>
+      <c r="L45" s="3"/>
       <c r="M45" s="3"/>
     </row>
     <row r="46" ht="24" customHeight="1" spans="3:13">
       <c r="C46" s="3">
-        <v>3104</v>
-      </c>
-      <c r="D46" s="5" t="s">
+        <v>3101</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E46" s="3">
-        <v>1085</v>
-      </c>
-      <c r="F46" s="6">
-        <v>1104</v>
+        <v>1070</v>
+      </c>
+      <c r="F46" s="3">
+        <v>1084</v>
       </c>
       <c r="G46" s="3">
         <v>4</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
-      <c r="J46" s="9" t="s">
-        <v>55</v>
+      <c r="J46" s="8" t="s">
+        <v>52</v>
       </c>
       <c r="K46" s="3">
         <v>3</v>
@@ -2516,24 +2515,24 @@
     </row>
     <row r="47" ht="24" customHeight="1" spans="3:13">
       <c r="C47" s="3">
-        <v>3105</v>
-      </c>
-      <c r="D47" s="5" t="s">
+        <v>3102</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>51</v>
       </c>
       <c r="E47" s="3">
-        <v>1085</v>
-      </c>
-      <c r="F47" s="6">
-        <v>1104</v>
+        <v>1070</v>
+      </c>
+      <c r="F47" s="3">
+        <v>1084</v>
       </c>
       <c r="G47" s="3">
         <v>4</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
-      <c r="J47" s="9" t="s">
-        <v>56</v>
+      <c r="J47" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="K47" s="3">
         <v>3</v>
@@ -2545,230 +2544,262 @@
     </row>
     <row r="48" ht="24" customHeight="1" spans="3:13">
       <c r="C48" s="3">
-        <v>3106</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E48" s="6">
-        <v>1105</v>
+        <v>3103</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1070</v>
       </c>
       <c r="F48" s="3">
-        <v>1139</v>
+        <v>1084</v>
       </c>
       <c r="G48" s="3">
         <v>4</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
-      <c r="J48" s="9" t="s">
-        <v>58</v>
+      <c r="J48" s="8" t="s">
+        <v>54</v>
       </c>
       <c r="K48" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L48" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M48" s="3"/>
     </row>
     <row r="49" ht="24" customHeight="1" spans="3:13">
       <c r="C49" s="3">
-        <v>3107</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E49" s="6">
-        <v>1105</v>
-      </c>
-      <c r="F49" s="3">
-        <v>1139</v>
+        <v>3104</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1085</v>
+      </c>
+      <c r="F49" s="5">
+        <v>1104</v>
       </c>
       <c r="G49" s="3">
         <v>4</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
-      <c r="J49" s="9" t="s">
-        <v>59</v>
+      <c r="J49" s="8" t="s">
+        <v>55</v>
       </c>
       <c r="K49" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L49" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M49" s="3"/>
     </row>
     <row r="50" ht="24" customHeight="1" spans="3:13">
       <c r="C50" s="3">
-        <v>3108</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E50" s="6">
-        <v>1105</v>
-      </c>
-      <c r="F50" s="3">
-        <v>1139</v>
+        <v>3105</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E50" s="3">
+        <v>1085</v>
+      </c>
+      <c r="F50" s="5">
+        <v>1104</v>
       </c>
       <c r="G50" s="3">
         <v>4</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
-      <c r="J50" s="9" t="s">
-        <v>60</v>
+      <c r="J50" s="8" t="s">
+        <v>56</v>
       </c>
       <c r="K50" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L50" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M50" s="3"/>
     </row>
     <row r="51" ht="24" customHeight="1" spans="3:13">
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
+      <c r="C51" s="3">
+        <v>3106</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E51" s="5">
+        <v>1105</v>
+      </c>
+      <c r="F51" s="3">
+        <v>1139</v>
+      </c>
+      <c r="G51" s="3">
+        <v>4</v>
+      </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
-      <c r="J51" s="3"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3"/>
+      <c r="J51" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="K51" s="3">
+        <v>4</v>
+      </c>
+      <c r="L51" s="3">
+        <v>2</v>
+      </c>
       <c r="M51" s="3"/>
     </row>
-    <row r="52" ht="22" customHeight="1" spans="3:13">
+    <row r="52" ht="24" customHeight="1" spans="3:13">
       <c r="C52" s="3">
-        <v>3201</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1070</v>
+        <v>3107</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E52" s="5">
+        <v>1105</v>
       </c>
       <c r="F52" s="3">
         <v>1139</v>
       </c>
       <c r="G52" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
-      <c r="J52" s="9" t="s">
-        <v>62</v>
+      <c r="J52" s="8" t="s">
+        <v>59</v>
       </c>
       <c r="K52" s="3">
+        <v>4</v>
+      </c>
+      <c r="L52" s="3">
         <v>2</v>
       </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
       <c r="M52" s="3"/>
     </row>
-    <row r="53" ht="22" customHeight="1" spans="3:13">
+    <row r="53" ht="24" customHeight="1" spans="3:13">
       <c r="C53" s="3">
-        <v>3202</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E53" s="3">
-        <v>1070</v>
+        <v>3108</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E53" s="5">
+        <v>1105</v>
       </c>
       <c r="F53" s="3">
         <v>1139</v>
       </c>
       <c r="G53" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
-      <c r="J53" s="9" t="s">
-        <v>63</v>
+      <c r="J53" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="K53" s="3">
+        <v>4</v>
+      </c>
+      <c r="L53" s="3">
         <v>2</v>
       </c>
-      <c r="L53" s="3">
-        <v>0</v>
-      </c>
       <c r="M53" s="3"/>
     </row>
-    <row r="54" ht="22" customHeight="1" spans="3:13">
+    <row r="54" ht="24" customHeight="1" spans="3:13">
       <c r="C54" s="3">
-        <v>3203</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E54" s="3">
-        <v>1070</v>
+        <v>3109</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E54" s="5">
+        <v>1140</v>
       </c>
       <c r="F54" s="3">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G54" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
-      <c r="J54" s="9" t="s">
-        <v>52</v>
+      <c r="J54" s="8" t="s">
+        <v>58</v>
       </c>
       <c r="K54" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L54" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M54" s="3"/>
     </row>
     <row r="55" ht="24" customHeight="1" spans="3:13">
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
+      <c r="C55" s="3">
+        <v>3110</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E55" s="5">
+        <v>1140</v>
+      </c>
+      <c r="F55" s="3">
+        <v>1175</v>
+      </c>
+      <c r="G55" s="3">
+        <v>4</v>
+      </c>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
-      <c r="J55" s="3"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3"/>
+      <c r="J55" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="K55" s="3">
+        <v>8</v>
+      </c>
+      <c r="L55" s="3">
+        <v>4</v>
+      </c>
       <c r="M55" s="3"/>
     </row>
-    <row r="56" ht="22" customHeight="1" spans="3:13">
+    <row r="56" ht="24" customHeight="1" spans="3:13">
       <c r="C56" s="3">
-        <v>3301</v>
-      </c>
-      <c r="D56" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E56" s="3">
-        <v>1105</v>
+        <v>3111</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E56" s="5">
+        <v>1140</v>
       </c>
       <c r="F56" s="3">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G56" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
-      <c r="J56" s="9" t="s">
-        <v>63</v>
+      <c r="J56" s="8" t="s">
+        <v>60</v>
       </c>
       <c r="K56" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L56" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M56" s="3"/>
     </row>
@@ -2785,43 +2816,91 @@
       <c r="L57" s="3"/>
       <c r="M57" s="3"/>
     </row>
-    <row r="58" ht="24" customHeight="1" spans="3:13">
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
+    <row r="58" ht="22" customHeight="1" spans="3:13">
+      <c r="C58" s="3">
+        <v>3201</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1070</v>
+      </c>
+      <c r="F58" s="3">
+        <v>1175</v>
+      </c>
+      <c r="G58" s="3">
+        <v>3</v>
+      </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
-      <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
-      <c r="L58" s="3"/>
+      <c r="J58" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K58" s="3">
+        <v>2</v>
+      </c>
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
       <c r="M58" s="3"/>
     </row>
-    <row r="59" ht="24" customHeight="1" spans="3:13">
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
+    <row r="59" ht="22" customHeight="1" spans="3:13">
+      <c r="C59" s="3">
+        <v>3202</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1070</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1175</v>
+      </c>
+      <c r="G59" s="3">
+        <v>3</v>
+      </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
-      <c r="L59" s="3"/>
+      <c r="J59" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K59" s="3">
+        <v>2</v>
+      </c>
+      <c r="L59" s="3">
+        <v>0</v>
+      </c>
       <c r="M59" s="3"/>
     </row>
-    <row r="60" ht="24" customHeight="1" spans="3:13">
-      <c r="C60" s="3"/>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
+    <row r="60" ht="22" customHeight="1" spans="3:13">
+      <c r="C60" s="3">
+        <v>3203</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1070</v>
+      </c>
+      <c r="F60" s="3">
+        <v>1175</v>
+      </c>
+      <c r="G60" s="3">
+        <v>3</v>
+      </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
-      <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="3"/>
+      <c r="J60" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="K60" s="3">
+        <v>2</v>
+      </c>
+      <c r="L60" s="3">
+        <v>0</v>
+      </c>
       <c r="M60" s="3"/>
     </row>
     <row r="61" ht="24" customHeight="1" spans="3:13">
@@ -2837,17 +2916,33 @@
       <c r="L61" s="3"/>
       <c r="M61" s="3"/>
     </row>
-    <row r="62" ht="24" customHeight="1" spans="3:13">
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
+    <row r="62" ht="22" customHeight="1" spans="3:13">
+      <c r="C62" s="3">
+        <v>3301</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E62" s="3">
+        <v>1105</v>
+      </c>
+      <c r="F62" s="3">
+        <v>1175</v>
+      </c>
+      <c r="G62" s="3">
+        <v>2</v>
+      </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="3"/>
+      <c r="J62" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="K62" s="3">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
       <c r="M62" s="3"/>
     </row>
     <row r="63" ht="24" customHeight="1" spans="3:13">
@@ -3006,39 +3101,135 @@
       <c r="L74" s="3"/>
       <c r="M74" s="3"/>
     </row>
+    <row r="75" ht="24" customHeight="1" spans="3:13">
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="3"/>
+      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
+      <c r="J75" s="3"/>
+      <c r="K75" s="3"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" ht="24" customHeight="1" spans="3:13">
+      <c r="C76" s="3"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="3"/>
+      <c r="F76" s="3"/>
+      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
+      <c r="J76" s="3"/>
+      <c r="K76" s="3"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" ht="24" customHeight="1" spans="3:13">
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="78" ht="24" customHeight="1" spans="3:13">
+      <c r="C78" s="3"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="H78" s="3"/>
+      <c r="I78" s="3"/>
+      <c r="J78" s="3"/>
+      <c r="K78" s="3"/>
+      <c r="L78" s="3"/>
+      <c r="M78" s="3"/>
+    </row>
+    <row r="79" ht="24" customHeight="1" spans="3:13">
+      <c r="C79" s="3"/>
+      <c r="D79" s="3"/>
+      <c r="E79" s="3"/>
+      <c r="F79" s="3"/>
+      <c r="G79" s="3"/>
+      <c r="H79" s="3"/>
+      <c r="I79" s="3"/>
+      <c r="J79" s="3"/>
+      <c r="K79" s="3"/>
+      <c r="L79" s="3"/>
+      <c r="M79" s="3"/>
+    </row>
+    <row r="80" ht="24" customHeight="1" spans="3:13">
+      <c r="C80" s="3"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="3"/>
+      <c r="G80" s="3"/>
+      <c r="H80" s="3"/>
+      <c r="I80" s="3"/>
+      <c r="J80" s="3"/>
+      <c r="K80" s="3"/>
+      <c r="L80" s="3"/>
+      <c r="M80" s="3"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="F36">
+    <cfRule type="duplicateValues" dxfId="0" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F37">
+    <cfRule type="duplicateValues" dxfId="0" priority="17"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E38">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E39">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E40">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E41">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E42">
+    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E43">
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F37">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
+  <conditionalFormatting sqref="F49">
+    <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E38">
-    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  <conditionalFormatting sqref="F50">
+    <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E39">
-    <cfRule type="duplicateValues" dxfId="0" priority="9"/>
+  <conditionalFormatting sqref="E51">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E40">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
+  <conditionalFormatting sqref="E52">
+    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F46">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+  <conditionalFormatting sqref="E53">
+    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F47">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E48">
+  <conditionalFormatting sqref="E54">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E49">
+  <conditionalFormatting sqref="E55">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E50">
+  <conditionalFormatting sqref="E56">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F36 F37 E38 E39 E40 F46 F47 E48 E49 E50" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E41 E42 E43 E54 E55 E56 E38:E40 E51:E53 F36:F37 F49:F50" errorStyle="warning">
       <formula1>COUNTIF($C:$C,E36)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:M5" errorStyle="warning">

--- a/Excel/PlayerModel.xlsx
+++ b/Excel/PlayerModel.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="69">
   <si>
     <t>ID</t>
   </si>
@@ -180,6 +180,18 @@
   </si>
   <si>
     <t>1002,2002,1004,2007,1010,2010</t>
+  </si>
+  <si>
+    <t>神级</t>
+  </si>
+  <si>
+    <t>2002,2003,2007,2008,2009,2010,2012</t>
+  </si>
+  <si>
+    <t>1004,1007,1008,1010,1012</t>
+  </si>
+  <si>
+    <t>3002,3001,2007,3012,1008</t>
   </si>
   <si>
     <t>王级</t>
@@ -1202,7 +1214,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q84"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -2459,159 +2471,143 @@
       <c r="M43" s="3"/>
     </row>
     <row r="44" ht="24" customHeight="1" spans="3:13">
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
+      <c r="C44" s="3">
+        <v>3024</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E44" s="5">
+        <v>1176</v>
+      </c>
+      <c r="F44" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G44" s="3">
+        <v>5</v>
+      </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
+      <c r="J44" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="K44" s="3">
+        <v>15</v>
+      </c>
+      <c r="L44" s="3">
+        <v>15</v>
+      </c>
       <c r="M44" s="3"/>
     </row>
     <row r="45" ht="24" customHeight="1" spans="3:13">
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
+      <c r="C45" s="3">
+        <v>3025</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E45" s="5">
+        <v>1176</v>
+      </c>
+      <c r="F45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G45" s="3">
+        <v>5</v>
+      </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
-      <c r="J45" s="3"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3"/>
+      <c r="J45" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="K45" s="3">
+        <v>15</v>
+      </c>
+      <c r="L45" s="3">
+        <v>15</v>
+      </c>
       <c r="M45" s="3"/>
     </row>
     <row r="46" ht="24" customHeight="1" spans="3:13">
       <c r="C46" s="3">
-        <v>3101</v>
+        <v>3026</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E46" s="3">
-        <v>1070</v>
+      <c r="E46" s="5">
+        <v>1176</v>
       </c>
       <c r="F46" s="3">
-        <v>1084</v>
+        <v>2000</v>
       </c>
       <c r="G46" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K46" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="L46" s="3">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M46" s="3"/>
     </row>
     <row r="47" ht="24" customHeight="1" spans="3:13">
-      <c r="C47" s="3">
-        <v>3102</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E47" s="3">
-        <v>1070</v>
-      </c>
-      <c r="F47" s="3">
-        <v>1084</v>
-      </c>
-      <c r="G47" s="3">
-        <v>4</v>
-      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
-      <c r="J47" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="K47" s="3">
-        <v>3</v>
-      </c>
-      <c r="L47" s="3">
-        <v>1</v>
-      </c>
+      <c r="J47" s="3"/>
+      <c r="K47" s="3"/>
+      <c r="L47" s="3"/>
       <c r="M47" s="3"/>
     </row>
     <row r="48" ht="24" customHeight="1" spans="3:13">
-      <c r="C48" s="3">
-        <v>3103</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E48" s="3">
-        <v>1070</v>
-      </c>
-      <c r="F48" s="3">
-        <v>1084</v>
-      </c>
-      <c r="G48" s="3">
-        <v>4</v>
-      </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
-      <c r="J48" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="K48" s="3">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3">
-        <v>1</v>
-      </c>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
       <c r="M48" s="3"/>
     </row>
     <row r="49" ht="24" customHeight="1" spans="3:13">
-      <c r="C49" s="3">
-        <v>3104</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E49" s="3">
-        <v>1085</v>
-      </c>
-      <c r="F49" s="5">
-        <v>1104</v>
-      </c>
-      <c r="G49" s="3">
-        <v>4</v>
-      </c>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
-      <c r="J49" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="K49" s="3">
-        <v>3</v>
-      </c>
-      <c r="L49" s="3">
-        <v>1</v>
-      </c>
+      <c r="J49" s="3"/>
+      <c r="K49" s="3"/>
+      <c r="L49" s="3"/>
       <c r="M49" s="3"/>
     </row>
     <row r="50" ht="24" customHeight="1" spans="3:13">
       <c r="C50" s="3">
-        <v>3105</v>
+        <v>3101</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E50" s="3">
-        <v>1085</v>
-      </c>
-      <c r="F50" s="5">
-        <v>1104</v>
+        <v>1070</v>
+      </c>
+      <c r="F50" s="3">
+        <v>1084</v>
       </c>
       <c r="G50" s="3">
         <v>4</v>
@@ -2631,16 +2627,16 @@
     </row>
     <row r="51" ht="24" customHeight="1" spans="3:13">
       <c r="C51" s="3">
-        <v>3106</v>
+        <v>3102</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E51" s="5">
-        <v>1105</v>
+        <v>55</v>
+      </c>
+      <c r="E51" s="3">
+        <v>1070</v>
       </c>
       <c r="F51" s="3">
-        <v>1139</v>
+        <v>1084</v>
       </c>
       <c r="G51" s="3">
         <v>4</v>
@@ -2648,28 +2644,28 @@
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K51" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L51" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M51" s="3"/>
     </row>
     <row r="52" ht="24" customHeight="1" spans="3:13">
       <c r="C52" s="3">
-        <v>3107</v>
+        <v>3103</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E52" s="5">
-        <v>1105</v>
+        <v>55</v>
+      </c>
+      <c r="E52" s="3">
+        <v>1070</v>
       </c>
       <c r="F52" s="3">
-        <v>1139</v>
+        <v>1084</v>
       </c>
       <c r="G52" s="3">
         <v>4</v>
@@ -2677,28 +2673,28 @@
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K52" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L52" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M52" s="3"/>
     </row>
     <row r="53" ht="24" customHeight="1" spans="3:13">
       <c r="C53" s="3">
-        <v>3108</v>
+        <v>3104</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E53" s="5">
-        <v>1105</v>
-      </c>
-      <c r="F53" s="3">
-        <v>1139</v>
+        <v>55</v>
+      </c>
+      <c r="E53" s="3">
+        <v>1085</v>
+      </c>
+      <c r="F53" s="5">
+        <v>1104</v>
       </c>
       <c r="G53" s="3">
         <v>4</v>
@@ -2706,28 +2702,28 @@
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K53" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L53" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M53" s="3"/>
     </row>
     <row r="54" ht="24" customHeight="1" spans="3:13">
       <c r="C54" s="3">
-        <v>3109</v>
+        <v>3105</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E54" s="5">
-        <v>1140</v>
-      </c>
-      <c r="F54" s="3">
-        <v>1175</v>
+        <v>55</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1085</v>
+      </c>
+      <c r="F54" s="5">
+        <v>1104</v>
       </c>
       <c r="G54" s="3">
         <v>4</v>
@@ -2735,28 +2731,28 @@
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K54" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L54" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M54" s="3"/>
     </row>
     <row r="55" ht="24" customHeight="1" spans="3:13">
       <c r="C55" s="3">
-        <v>3110</v>
+        <v>3106</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E55" s="5">
-        <v>1140</v>
+        <v>1105</v>
       </c>
       <c r="F55" s="3">
-        <v>1175</v>
+        <v>1139</v>
       </c>
       <c r="G55" s="3">
         <v>4</v>
@@ -2764,28 +2760,28 @@
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K55" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L55" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M55" s="3"/>
     </row>
     <row r="56" ht="24" customHeight="1" spans="3:13">
       <c r="C56" s="3">
-        <v>3111</v>
+        <v>3107</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E56" s="5">
-        <v>1140</v>
+        <v>1105</v>
       </c>
       <c r="F56" s="3">
-        <v>1175</v>
+        <v>1139</v>
       </c>
       <c r="G56" s="3">
         <v>4</v>
@@ -2793,44 +2789,60 @@
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K56" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L56" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M56" s="3"/>
     </row>
     <row r="57" ht="24" customHeight="1" spans="3:13">
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
+      <c r="C57" s="3">
+        <v>3108</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E57" s="5">
+        <v>1105</v>
+      </c>
+      <c r="F57" s="3">
+        <v>1139</v>
+      </c>
+      <c r="G57" s="3">
+        <v>4</v>
+      </c>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-      <c r="L57" s="3"/>
+      <c r="J57" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="K57" s="3">
+        <v>4</v>
+      </c>
+      <c r="L57" s="3">
+        <v>2</v>
+      </c>
       <c r="M57" s="3"/>
     </row>
-    <row r="58" ht="22" customHeight="1" spans="3:13">
+    <row r="58" ht="24" customHeight="1" spans="3:13">
       <c r="C58" s="3">
-        <v>3201</v>
+        <v>3109</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E58" s="3">
-        <v>1070</v>
+      <c r="E58" s="5">
+        <v>1140</v>
       </c>
       <c r="F58" s="3">
         <v>1175</v>
       </c>
       <c r="G58" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
@@ -2838,28 +2850,28 @@
         <v>62</v>
       </c>
       <c r="K58" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M58" s="3"/>
     </row>
-    <row r="59" ht="22" customHeight="1" spans="3:13">
+    <row r="59" ht="24" customHeight="1" spans="3:13">
       <c r="C59" s="3">
-        <v>3202</v>
+        <v>3110</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E59" s="3">
-        <v>1070</v>
+      <c r="E59" s="5">
+        <v>1140</v>
       </c>
       <c r="F59" s="3">
         <v>1175</v>
       </c>
       <c r="G59" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
@@ -2867,39 +2879,39 @@
         <v>63</v>
       </c>
       <c r="K59" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L59" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M59" s="3"/>
     </row>
-    <row r="60" ht="22" customHeight="1" spans="3:13">
+    <row r="60" ht="24" customHeight="1" spans="3:13">
       <c r="C60" s="3">
-        <v>3203</v>
+        <v>3111</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E60" s="3">
-        <v>1070</v>
+      <c r="E60" s="5">
+        <v>1140</v>
       </c>
       <c r="F60" s="3">
         <v>1175</v>
       </c>
       <c r="G60" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="8" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="K60" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L60" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M60" s="3"/>
     </row>
@@ -2918,57 +2930,89 @@
     </row>
     <row r="62" ht="22" customHeight="1" spans="3:13">
       <c r="C62" s="3">
-        <v>3301</v>
+        <v>3201</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E62" s="3">
-        <v>1105</v>
+        <v>1070</v>
       </c>
       <c r="F62" s="3">
         <v>1175</v>
       </c>
       <c r="G62" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="8" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K62" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
       <c r="M62" s="3"/>
     </row>
-    <row r="63" ht="24" customHeight="1" spans="3:13">
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
+    <row r="63" ht="22" customHeight="1" spans="3:13">
+      <c r="C63" s="3">
+        <v>3202</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E63" s="3">
+        <v>1070</v>
+      </c>
+      <c r="F63" s="3">
+        <v>1175</v>
+      </c>
+      <c r="G63" s="3">
+        <v>3</v>
+      </c>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
-      <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
-      <c r="L63" s="3"/>
+      <c r="J63" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K63" s="3">
+        <v>2</v>
+      </c>
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
       <c r="M63" s="3"/>
     </row>
-    <row r="64" ht="24" customHeight="1" spans="3:13">
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
+    <row r="64" ht="22" customHeight="1" spans="3:13">
+      <c r="C64" s="3">
+        <v>3203</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E64" s="3">
+        <v>1070</v>
+      </c>
+      <c r="F64" s="3">
+        <v>1175</v>
+      </c>
+      <c r="G64" s="3">
+        <v>3</v>
+      </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="3"/>
+      <c r="J64" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="K64" s="3">
+        <v>2</v>
+      </c>
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
       <c r="M64" s="3"/>
     </row>
     <row r="65" ht="24" customHeight="1" spans="3:13">
@@ -2984,17 +3028,33 @@
       <c r="L65" s="3"/>
       <c r="M65" s="3"/>
     </row>
-    <row r="66" ht="24" customHeight="1" spans="3:13">
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="G66" s="3"/>
+    <row r="66" ht="22" customHeight="1" spans="3:13">
+      <c r="C66" s="3">
+        <v>3301</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1105</v>
+      </c>
+      <c r="F66" s="3">
+        <v>1175</v>
+      </c>
+      <c r="G66" s="3">
+        <v>2</v>
+      </c>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="3"/>
+      <c r="J66" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="K66" s="3">
+        <v>0</v>
+      </c>
+      <c r="L66" s="3">
+        <v>0</v>
+      </c>
       <c r="M66" s="3"/>
     </row>
     <row r="67" ht="24" customHeight="1" spans="3:13">
@@ -3179,57 +3239,118 @@
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
     </row>
+    <row r="81" ht="24" customHeight="1" spans="3:13">
+      <c r="C81" s="3"/>
+      <c r="D81" s="3"/>
+      <c r="E81" s="3"/>
+      <c r="F81" s="3"/>
+      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="3"/>
+      <c r="J81" s="3"/>
+      <c r="K81" s="3"/>
+      <c r="L81" s="3"/>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" ht="24" customHeight="1" spans="3:13">
+      <c r="C82" s="3"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="3"/>
+      <c r="F82" s="3"/>
+      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3"/>
+      <c r="J82" s="3"/>
+      <c r="K82" s="3"/>
+      <c r="L82" s="3"/>
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" ht="24" customHeight="1" spans="3:13">
+      <c r="C83" s="3"/>
+      <c r="D83" s="3"/>
+      <c r="E83" s="3"/>
+      <c r="F83" s="3"/>
+      <c r="G83" s="3"/>
+      <c r="H83" s="3"/>
+      <c r="I83" s="3"/>
+      <c r="J83" s="3"/>
+      <c r="K83" s="3"/>
+      <c r="L83" s="3"/>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" ht="24" customHeight="1" spans="3:13">
+      <c r="C84" s="3"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="3"/>
+      <c r="F84" s="3"/>
+      <c r="G84" s="3"/>
+      <c r="H84" s="3"/>
+      <c r="I84" s="3"/>
+      <c r="J84" s="3"/>
+      <c r="K84" s="3"/>
+      <c r="L84" s="3"/>
+      <c r="M84" s="3"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="F36">
+    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F37">
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E38">
+    <cfRule type="duplicateValues" dxfId="0" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E39">
+    <cfRule type="duplicateValues" dxfId="0" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E40">
+    <cfRule type="duplicateValues" dxfId="0" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E41">
+    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E42">
+    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E43">
+    <cfRule type="duplicateValues" dxfId="0" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E44">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E45">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E46">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F53">
+    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F54">
     <cfRule type="duplicateValues" dxfId="0" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F37">
+  <conditionalFormatting sqref="E55">
     <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E38">
-    <cfRule type="duplicateValues" dxfId="0" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E39">
-    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E40">
-    <cfRule type="duplicateValues" dxfId="0" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E41">
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E42">
-    <cfRule type="duplicateValues" dxfId="0" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E43">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F49">
+  <conditionalFormatting sqref="E56">
     <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F50">
+  <conditionalFormatting sqref="E57">
     <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E51">
-    <cfRule type="duplicateValues" dxfId="0" priority="14"/>
+  <conditionalFormatting sqref="E58">
+    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E52">
-    <cfRule type="duplicateValues" dxfId="0" priority="13"/>
+  <conditionalFormatting sqref="E59">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="0" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E54">
-    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E55">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E56">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="E60">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E41 E42 E43 E54 E55 E56 E38:E40 E51:E53 F36:F37 F49:F50" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E38:E46 E55:E60 F36:F37 F53:F54" errorStyle="warning">
       <formula1>COUNTIF($C:$C,E36)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:M5" errorStyle="warning">

--- a/Excel/PlayerModel.xlsx
+++ b/Excel/PlayerModel.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="70">
   <si>
     <t>ID</t>
   </si>
@@ -185,10 +185,13 @@
     <t>神级</t>
   </si>
   <si>
-    <t>2002,2003,2007,2008,2009,2010,2012</t>
+    <t>2002,2003,2007,2008,2009,2012</t>
   </si>
   <si>
     <t>1004,1007,1008,1010,1012</t>
+  </si>
+  <si>
+    <t>#</t>
   </si>
   <si>
     <t>3002,3001,2007,3012,1008</t>
@@ -2528,7 +2531,13 @@
       </c>
       <c r="M45" s="3"/>
     </row>
-    <row r="46" ht="24" customHeight="1" spans="3:13">
+    <row r="46" ht="24" customHeight="1" spans="1:13">
+      <c r="A46" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="C46" s="3">
         <v>3026</v>
       </c>
@@ -2547,7 +2556,7 @@
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K46" s="3">
         <v>15</v>
@@ -2601,7 +2610,7 @@
         <v>3101</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E50" s="3">
         <v>1070</v>
@@ -2615,7 +2624,7 @@
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K50" s="3">
         <v>3</v>
@@ -2630,7 +2639,7 @@
         <v>3102</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E51" s="3">
         <v>1070</v>
@@ -2644,7 +2653,7 @@
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K51" s="3">
         <v>3</v>
@@ -2659,7 +2668,7 @@
         <v>3103</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E52" s="3">
         <v>1070</v>
@@ -2673,7 +2682,7 @@
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K52" s="3">
         <v>3</v>
@@ -2688,7 +2697,7 @@
         <v>3104</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E53" s="3">
         <v>1085</v>
@@ -2702,7 +2711,7 @@
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K53" s="3">
         <v>3</v>
@@ -2717,7 +2726,7 @@
         <v>3105</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E54" s="3">
         <v>1085</v>
@@ -2731,7 +2740,7 @@
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K54" s="3">
         <v>3</v>
@@ -2746,7 +2755,7 @@
         <v>3106</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E55" s="5">
         <v>1105</v>
@@ -2760,7 +2769,7 @@
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K55" s="3">
         <v>4</v>
@@ -2775,7 +2784,7 @@
         <v>3107</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E56" s="5">
         <v>1105</v>
@@ -2789,7 +2798,7 @@
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K56" s="3">
         <v>4</v>
@@ -2804,7 +2813,7 @@
         <v>3108</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E57" s="5">
         <v>1105</v>
@@ -2818,7 +2827,7 @@
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K57" s="3">
         <v>4</v>
@@ -2833,7 +2842,7 @@
         <v>3109</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E58" s="5">
         <v>1140</v>
@@ -2847,7 +2856,7 @@
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K58" s="3">
         <v>8</v>
@@ -2862,7 +2871,7 @@
         <v>3110</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E59" s="5">
         <v>1140</v>
@@ -2876,7 +2885,7 @@
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K59" s="3">
         <v>8</v>
@@ -2891,7 +2900,7 @@
         <v>3111</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E60" s="5">
         <v>1140</v>
@@ -2905,7 +2914,7 @@
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K60" s="3">
         <v>8</v>
@@ -2933,7 +2942,7 @@
         <v>3201</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E62" s="3">
         <v>1070</v>
@@ -2947,7 +2956,7 @@
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K62" s="3">
         <v>2</v>
@@ -2962,7 +2971,7 @@
         <v>3202</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E63" s="3">
         <v>1070</v>
@@ -2976,7 +2985,7 @@
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K63" s="3">
         <v>2</v>
@@ -2991,7 +3000,7 @@
         <v>3203</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E64" s="3">
         <v>1070</v>
@@ -3005,7 +3014,7 @@
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K64" s="3">
         <v>2</v>
@@ -3033,7 +3042,7 @@
         <v>3301</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E66" s="3">
         <v>1105</v>
@@ -3047,7 +3056,7 @@
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
       <c r="J66" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K66" s="3">
         <v>0</v>

--- a/Excel/PlayerModel.xlsx
+++ b/Excel/PlayerModel.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WrittenLegend\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -27,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="68">
   <si>
     <t>ID</t>
   </si>
@@ -113,12 +118,6 @@
     <t>剧毒</t>
   </si>
   <si>
-    <t>召唤</t>
-  </si>
-  <si>
-    <t>3004,13002</t>
-  </si>
-  <si>
     <t>火神</t>
   </si>
   <si>
@@ -140,7 +139,7 @@
     <t>2001,2007,1007</t>
   </si>
   <si>
-    <t>3002,3007,1009</t>
+    <t>3002,1009</t>
   </si>
   <si>
     <t>1002,2003,2002</t>
@@ -883,9 +882,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
@@ -1217,7 +1216,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6.875" style="2" customWidth="1"/>
@@ -1387,7 +1386,7 @@
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" ht="24" customHeight="1" spans="3:13">
+    <row r="6" ht="24" customHeight="1" spans="1:17">
       <c r="C6" s="3">
         <v>1</v>
       </c>
@@ -1416,7 +1415,7 @@
       </c>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" ht="24" customHeight="1" spans="3:13">
+    <row r="7" ht="24" customHeight="1" spans="1:17">
       <c r="C7" s="3">
         <v>2</v>
       </c>
@@ -1445,7 +1444,7 @@
       </c>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" ht="24" customHeight="1" spans="3:13">
+    <row r="8" ht="24" customHeight="1" spans="1:17">
       <c r="C8" s="3">
         <v>3</v>
       </c>
@@ -1474,7 +1473,7 @@
       </c>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="3:13">
+    <row r="9" ht="24" customHeight="1" spans="1:17">
       <c r="C9" s="3">
         <v>4</v>
       </c>
@@ -1503,7 +1502,7 @@
       </c>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" ht="24" customHeight="1" spans="3:13">
+    <row r="10" ht="24" customHeight="1" spans="1:17">
       <c r="C10" s="3">
         <v>5</v>
       </c>
@@ -1532,7 +1531,7 @@
       </c>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="3:13">
+    <row r="11" ht="24" customHeight="1" spans="1:17">
       <c r="C11" s="3">
         <v>6</v>
       </c>
@@ -1561,7 +1560,7 @@
       </c>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="3:13">
+    <row r="12" ht="24" customHeight="1" spans="1:17">
       <c r="C12" s="3">
         <v>7</v>
       </c>
@@ -1590,7 +1589,7 @@
       </c>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" ht="24" customHeight="1" spans="3:13">
+    <row r="13" ht="24" customHeight="1" spans="1:17">
       <c r="C13" s="3">
         <v>8</v>
       </c>
@@ -1619,7 +1618,7 @@
       </c>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" ht="24" customHeight="1" spans="3:13">
+    <row r="14" ht="24" customHeight="1" spans="1:17">
       <c r="C14" s="3">
         <v>9</v>
       </c>
@@ -1648,7 +1647,7 @@
       </c>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="3:13">
+    <row r="15" ht="24" customHeight="1" spans="1:17">
       <c r="C15" s="3">
         <v>10</v>
       </c>
@@ -1677,7 +1676,7 @@
       </c>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" ht="24" customHeight="1" spans="3:13">
+    <row r="16" ht="24" customHeight="1" spans="1:17">
       <c r="C16" s="3">
         <v>11</v>
       </c>
@@ -1724,7 +1723,7 @@
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
-      <c r="J17" s="8" t="s">
+      <c r="J17" s="9" t="s">
         <v>29</v>
       </c>
       <c r="K17" s="3">
@@ -1753,71 +1752,71 @@
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="9" t="s">
+      <c r="J18" s="3"/>
+      <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3"/>
     </row>
     <row r="19" ht="24" customHeight="1" spans="3:13">
-      <c r="C19" s="3">
-        <v>14</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>1069</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0</v>
-      </c>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
-      <c r="K19" s="3">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>33</v>
-      </c>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
     </row>
     <row r="20" ht="24" customHeight="1" spans="3:13">
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
+      <c r="C20" s="3">
+        <v>3001</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1070</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1070</v>
+      </c>
+      <c r="G20" s="3">
+        <v>5</v>
+      </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
+      <c r="J20" s="3">
+        <v>1001</v>
+      </c>
+      <c r="K20" s="3">
+        <v>4</v>
+      </c>
+      <c r="L20" s="3">
+        <v>4</v>
+      </c>
       <c r="M20" s="3"/>
     </row>
     <row r="21" ht="24" customHeight="1" spans="3:13">
       <c r="C21" s="3">
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E21" s="3">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F21" s="3">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="G21" s="3">
         <v>5</v>
@@ -1825,7 +1824,7 @@
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3">
-        <v>1001</v>
+        <v>2001</v>
       </c>
       <c r="K21" s="3">
         <v>4</v>
@@ -1837,16 +1836,16 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="3:13">
       <c r="C22" s="3">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E22" s="3">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="F22" s="3">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="G22" s="3">
         <v>5</v>
@@ -1854,7 +1853,7 @@
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3">
-        <v>2001</v>
+        <v>3002</v>
       </c>
       <c r="K22" s="3">
         <v>4</v>
@@ -1866,16 +1865,16 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="3:13">
       <c r="C23" s="3">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E23" s="3">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="F23" s="3">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="G23" s="3">
         <v>5</v>
@@ -1883,7 +1882,7 @@
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3">
-        <v>3002</v>
+        <v>2002</v>
       </c>
       <c r="K23" s="3">
         <v>4</v>
@@ -1895,16 +1894,16 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="3:13">
       <c r="C24" s="3">
-        <v>3004</v>
+        <v>3005</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E24" s="3">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F24" s="3">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="G24" s="3">
         <v>5</v>
@@ -1912,7 +1911,7 @@
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3">
-        <v>2002</v>
+        <v>1002</v>
       </c>
       <c r="K24" s="3">
         <v>4</v>
@@ -1924,24 +1923,24 @@
     </row>
     <row r="25" ht="24" customHeight="1" spans="3:13">
       <c r="C25" s="3">
-        <v>3005</v>
+        <v>3006</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E25" s="3">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F25" s="3">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="G25" s="3">
         <v>5</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-      <c r="J25" s="3">
-        <v>1002</v>
+      <c r="J25" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="K25" s="3">
         <v>4</v>
@@ -1953,16 +1952,16 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="3:13">
       <c r="C26" s="3">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E26" s="3">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F26" s="3">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="G26" s="3">
         <v>5</v>
@@ -1970,7 +1969,7 @@
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
       <c r="J26" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K26" s="3">
         <v>4</v>
@@ -1982,16 +1981,16 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="3:13">
       <c r="C27" s="3">
-        <v>3007</v>
+        <v>3008</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E27" s="3">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="F27" s="3">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="G27" s="3">
         <v>5</v>
@@ -1999,7 +1998,7 @@
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K27" s="3">
         <v>4</v>
@@ -2011,16 +2010,16 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="3:13">
       <c r="C28" s="3">
-        <v>3008</v>
+        <v>3009</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E28" s="3">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F28" s="3">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="G28" s="3">
         <v>5</v>
@@ -2028,7 +2027,7 @@
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K28" s="3">
         <v>4</v>
@@ -2040,16 +2039,16 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="3:13">
       <c r="C29" s="3">
-        <v>3009</v>
+        <v>3010</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E29" s="3">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F29" s="3">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="G29" s="3">
         <v>5</v>
@@ -2057,7 +2056,7 @@
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K29" s="3">
         <v>4</v>
@@ -2069,16 +2068,16 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="3:13">
       <c r="C30" s="3">
-        <v>3010</v>
+        <v>3011</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E30" s="3">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F30" s="3">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="G30" s="3">
         <v>5</v>
@@ -2086,7 +2085,7 @@
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K30" s="3">
         <v>4</v>
@@ -2098,16 +2097,16 @@
     </row>
     <row r="31" ht="24" customHeight="1" spans="3:13">
       <c r="C31" s="3">
-        <v>3011</v>
+        <v>3012</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E31" s="3">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F31" s="3">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="G31" s="3">
         <v>5</v>
@@ -2115,7 +2114,7 @@
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K31" s="3">
         <v>4</v>
@@ -2127,16 +2126,16 @@
     </row>
     <row r="32" ht="24" customHeight="1" spans="3:13">
       <c r="C32" s="3">
-        <v>3012</v>
+        <v>3013</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E32" s="3">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F32" s="3">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="G32" s="3">
         <v>5</v>
@@ -2144,7 +2143,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
       <c r="J32" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K32" s="3">
         <v>4</v>
@@ -2154,26 +2153,26 @@
       </c>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" ht="24" customHeight="1" spans="3:13">
+    <row r="33" ht="24" customHeight="1" spans="1:13">
       <c r="C33" s="3">
-        <v>3013</v>
+        <v>3014</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E33" s="3">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F33" s="3">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="G33" s="3">
         <v>5</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
-      <c r="J33" s="8" t="s">
-        <v>42</v>
+      <c r="J33" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="K33" s="3">
         <v>4</v>
@@ -2183,26 +2182,26 @@
       </c>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" ht="24" customHeight="1" spans="3:13">
+    <row r="34" ht="24" customHeight="1" spans="1:13">
       <c r="C34" s="3">
-        <v>3014</v>
+        <v>3015</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E34" s="3">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F34" s="3">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="G34" s="3">
         <v>5</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="10" t="s">
-        <v>43</v>
+      <c r="J34" s="8" t="s">
+        <v>42</v>
       </c>
       <c r="K34" s="3">
         <v>4</v>
@@ -2212,18 +2211,18 @@
       </c>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" ht="24" customHeight="1" spans="3:13">
+    <row r="35" ht="24" customHeight="1" spans="1:13">
       <c r="C35" s="3">
-        <v>3015</v>
+        <v>3016</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E35" s="3">
-        <v>1084</v>
-      </c>
-      <c r="F35" s="3">
-        <v>1084</v>
+        <v>1085</v>
+      </c>
+      <c r="F35" s="7">
+        <v>1104</v>
       </c>
       <c r="G35" s="3">
         <v>5</v>
@@ -2231,7 +2230,7 @@
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K35" s="3">
         <v>4</v>
@@ -2241,17 +2240,17 @@
       </c>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" ht="24" customHeight="1" spans="3:13">
+    <row r="36" ht="24" customHeight="1" spans="1:13">
       <c r="C36" s="3">
-        <v>3016</v>
+        <v>3017</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E36" s="3">
         <v>1085</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="7">
         <v>1104</v>
       </c>
       <c r="G36" s="3">
@@ -2260,28 +2259,28 @@
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="K36" s="3">
+        <v>4</v>
+      </c>
+      <c r="L36" s="3">
+        <v>4</v>
+      </c>
+      <c r="M36" s="3"/>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="1:13">
+      <c r="C37" s="3">
+        <v>3018</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="K36" s="3">
-        <v>4</v>
-      </c>
-      <c r="L36" s="3">
-        <v>4</v>
-      </c>
-      <c r="M36" s="3"/>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="3:13">
-      <c r="C37" s="3">
-        <v>3017</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E37" s="3">
-        <v>1085</v>
-      </c>
-      <c r="F37" s="5">
-        <v>1104</v>
+      <c r="E37" s="7">
+        <v>1105</v>
+      </c>
+      <c r="F37" s="3">
+        <v>1139</v>
       </c>
       <c r="G37" s="3">
         <v>5</v>
@@ -2292,21 +2291,21 @@
         <v>46</v>
       </c>
       <c r="K37" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L37" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" ht="24" customHeight="1" spans="3:13">
+    <row r="38" ht="24" customHeight="1" spans="1:13">
       <c r="C38" s="3">
-        <v>3018</v>
+        <v>3019</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E38" s="5">
+        <v>45</v>
+      </c>
+      <c r="E38" s="7">
         <v>1105</v>
       </c>
       <c r="F38" s="3">
@@ -2318,7 +2317,7 @@
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K38" s="3">
         <v>5</v>
@@ -2328,14 +2327,14 @@
       </c>
       <c r="M38" s="3"/>
     </row>
-    <row r="39" ht="24" customHeight="1" spans="3:13">
+    <row r="39" ht="24" customHeight="1" spans="1:13">
       <c r="C39" s="3">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E39" s="5">
+        <v>45</v>
+      </c>
+      <c r="E39" s="7">
         <v>1105</v>
       </c>
       <c r="F39" s="3">
@@ -2347,7 +2346,7 @@
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K39" s="3">
         <v>5</v>
@@ -2357,18 +2356,18 @@
       </c>
       <c r="M39" s="3"/>
     </row>
-    <row r="40" ht="24" customHeight="1" spans="3:13">
+    <row r="40" ht="24" customHeight="1" spans="1:13">
       <c r="C40" s="3">
-        <v>3020</v>
+        <v>3021</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E40" s="5">
-        <v>1105</v>
+        <v>45</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1140</v>
       </c>
       <c r="F40" s="3">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G40" s="3">
         <v>5</v>
@@ -2376,24 +2375,24 @@
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="8" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K40" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L40" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M40" s="3"/>
     </row>
-    <row r="41" ht="24" customHeight="1" spans="3:13">
+    <row r="41" ht="24" customHeight="1" spans="1:13">
       <c r="C41" s="3">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E41" s="5">
+        <v>45</v>
+      </c>
+      <c r="E41" s="7">
         <v>1140</v>
       </c>
       <c r="F41" s="3">
@@ -2405,7 +2404,7 @@
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K41" s="3">
         <v>10</v>
@@ -2415,14 +2414,14 @@
       </c>
       <c r="M41" s="3"/>
     </row>
-    <row r="42" ht="24" customHeight="1" spans="3:13">
+    <row r="42" ht="24" customHeight="1" spans="1:13">
       <c r="C42" s="3">
-        <v>3022</v>
+        <v>3023</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E42" s="5">
+        <v>45</v>
+      </c>
+      <c r="E42" s="7">
         <v>1140</v>
       </c>
       <c r="F42" s="3">
@@ -2434,7 +2433,7 @@
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
       <c r="J42" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K42" s="3">
         <v>10</v>
@@ -2444,18 +2443,18 @@
       </c>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" ht="24" customHeight="1" spans="3:13">
+    <row r="43" ht="24" customHeight="1" spans="1:13">
       <c r="C43" s="3">
-        <v>3023</v>
+        <v>3024</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E43" s="5">
-        <v>1140</v>
+        <v>49</v>
+      </c>
+      <c r="E43" s="7">
+        <v>1176</v>
       </c>
       <c r="F43" s="3">
-        <v>1175</v>
+        <v>2000</v>
       </c>
       <c r="G43" s="3">
         <v>5</v>
@@ -2466,21 +2465,21 @@
         <v>50</v>
       </c>
       <c r="K43" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L43" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" ht="24" customHeight="1" spans="3:13">
+    <row r="44" ht="24" customHeight="1" spans="1:13">
       <c r="C44" s="3">
-        <v>3024</v>
+        <v>3025</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E44" s="5">
+        <v>49</v>
+      </c>
+      <c r="E44" s="7">
         <v>1176</v>
       </c>
       <c r="F44" s="3">
@@ -2492,7 +2491,7 @@
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K44" s="3">
         <v>15</v>
@@ -2502,14 +2501,20 @@
       </c>
       <c r="M44" s="3"/>
     </row>
-    <row r="45" ht="24" customHeight="1" spans="3:13">
+    <row r="45" ht="24" customHeight="1" spans="1:13">
+      <c r="A45" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="C45" s="3">
-        <v>3025</v>
+        <v>3026</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E45" s="5">
+        <v>49</v>
+      </c>
+      <c r="E45" s="7">
         <v>1176</v>
       </c>
       <c r="F45" s="3">
@@ -2532,41 +2537,19 @@
       <c r="M45" s="3"/>
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:13">
-      <c r="A46" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C46" s="3">
-        <v>3026</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E46" s="5">
-        <v>1176</v>
-      </c>
-      <c r="F46" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G46" s="3">
-        <v>5</v>
-      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
-      <c r="J46" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="K46" s="3">
-        <v>15</v>
-      </c>
-      <c r="L46" s="3">
-        <v>15</v>
-      </c>
+      <c r="J46" s="3"/>
+      <c r="K46" s="3"/>
+      <c r="L46" s="3"/>
       <c r="M46" s="3"/>
     </row>
-    <row r="47" ht="24" customHeight="1" spans="3:13">
+    <row r="47" ht="24" customHeight="1" spans="1:13">
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -2579,7 +2562,7 @@
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" ht="24" customHeight="1" spans="3:13">
+    <row r="48" ht="24" customHeight="1" spans="1:13">
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -2593,24 +2576,40 @@
       <c r="M48" s="3"/>
     </row>
     <row r="49" ht="24" customHeight="1" spans="3:13">
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
+      <c r="C49" s="3">
+        <v>3101</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E49" s="3">
+        <v>1070</v>
+      </c>
+      <c r="F49" s="3">
+        <v>1084</v>
+      </c>
+      <c r="G49" s="3">
+        <v>4</v>
+      </c>
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
-      <c r="J49" s="3"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3"/>
+      <c r="J49" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="K49" s="3">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3">
+        <v>1</v>
+      </c>
       <c r="M49" s="3"/>
     </row>
     <row r="50" ht="24" customHeight="1" spans="3:13">
       <c r="C50" s="3">
-        <v>3101</v>
+        <v>3102</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E50" s="3">
         <v>1070</v>
@@ -2624,7 +2623,7 @@
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K50" s="3">
         <v>3</v>
@@ -2636,10 +2635,10 @@
     </row>
     <row r="51" ht="24" customHeight="1" spans="3:13">
       <c r="C51" s="3">
-        <v>3102</v>
+        <v>3103</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E51" s="3">
         <v>1070</v>
@@ -2653,7 +2652,7 @@
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K51" s="3">
         <v>3</v>
@@ -2665,16 +2664,16 @@
     </row>
     <row r="52" ht="24" customHeight="1" spans="3:13">
       <c r="C52" s="3">
-        <v>3103</v>
+        <v>3104</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E52" s="3">
-        <v>1070</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1084</v>
+        <v>1085</v>
+      </c>
+      <c r="F52" s="7">
+        <v>1104</v>
       </c>
       <c r="G52" s="3">
         <v>4</v>
@@ -2682,7 +2681,7 @@
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K52" s="3">
         <v>3</v>
@@ -2694,15 +2693,15 @@
     </row>
     <row r="53" ht="24" customHeight="1" spans="3:13">
       <c r="C53" s="3">
-        <v>3104</v>
+        <v>3105</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E53" s="3">
         <v>1085</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53" s="7">
         <v>1104</v>
       </c>
       <c r="G53" s="3">
@@ -2711,7 +2710,7 @@
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K53" s="3">
         <v>3</v>
@@ -2723,16 +2722,16 @@
     </row>
     <row r="54" ht="24" customHeight="1" spans="3:13">
       <c r="C54" s="3">
-        <v>3105</v>
+        <v>3106</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E54" s="3">
-        <v>1085</v>
-      </c>
-      <c r="F54" s="5">
-        <v>1104</v>
+        <v>60</v>
+      </c>
+      <c r="E54" s="7">
+        <v>1105</v>
+      </c>
+      <c r="F54" s="3">
+        <v>1139</v>
       </c>
       <c r="G54" s="3">
         <v>4</v>
@@ -2743,21 +2742,21 @@
         <v>61</v>
       </c>
       <c r="K54" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L54" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M54" s="3"/>
     </row>
     <row r="55" ht="24" customHeight="1" spans="3:13">
       <c r="C55" s="3">
-        <v>3106</v>
+        <v>3107</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E55" s="5">
+        <v>60</v>
+      </c>
+      <c r="E55" s="7">
         <v>1105</v>
       </c>
       <c r="F55" s="3">
@@ -2769,7 +2768,7 @@
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
       <c r="J55" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K55" s="3">
         <v>4</v>
@@ -2781,12 +2780,12 @@
     </row>
     <row r="56" ht="24" customHeight="1" spans="3:13">
       <c r="C56" s="3">
-        <v>3107</v>
+        <v>3108</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E56" s="5">
+        <v>60</v>
+      </c>
+      <c r="E56" s="7">
         <v>1105</v>
       </c>
       <c r="F56" s="3">
@@ -2798,7 +2797,7 @@
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K56" s="3">
         <v>4</v>
@@ -2810,16 +2809,16 @@
     </row>
     <row r="57" ht="24" customHeight="1" spans="3:13">
       <c r="C57" s="3">
-        <v>3108</v>
+        <v>3109</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E57" s="5">
-        <v>1105</v>
+        <v>60</v>
+      </c>
+      <c r="E57" s="7">
+        <v>1140</v>
       </c>
       <c r="F57" s="3">
-        <v>1139</v>
+        <v>1175</v>
       </c>
       <c r="G57" s="3">
         <v>4</v>
@@ -2827,24 +2826,24 @@
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="8" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="K57" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L57" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M57" s="3"/>
     </row>
     <row r="58" ht="24" customHeight="1" spans="3:13">
       <c r="C58" s="3">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E58" s="5">
+        <v>60</v>
+      </c>
+      <c r="E58" s="7">
         <v>1140</v>
       </c>
       <c r="F58" s="3">
@@ -2856,7 +2855,7 @@
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K58" s="3">
         <v>8</v>
@@ -2868,12 +2867,12 @@
     </row>
     <row r="59" ht="24" customHeight="1" spans="3:13">
       <c r="C59" s="3">
-        <v>3110</v>
+        <v>3111</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E59" s="5">
+        <v>60</v>
+      </c>
+      <c r="E59" s="7">
         <v>1140</v>
       </c>
       <c r="F59" s="3">
@@ -2885,7 +2884,7 @@
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K59" s="3">
         <v>8</v>
@@ -2896,53 +2895,53 @@
       <c r="M59" s="3"/>
     </row>
     <row r="60" ht="24" customHeight="1" spans="3:13">
-      <c r="C60" s="3">
-        <v>3111</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E60" s="5">
-        <v>1140</v>
-      </c>
-      <c r="F60" s="3">
-        <v>1175</v>
-      </c>
-      <c r="G60" s="3">
-        <v>4</v>
-      </c>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+      <c r="E60" s="3"/>
+      <c r="F60" s="3"/>
+      <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
-      <c r="J60" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="K60" s="3">
-        <v>8</v>
-      </c>
-      <c r="L60" s="3">
-        <v>4</v>
-      </c>
+      <c r="J60" s="3"/>
+      <c r="K60" s="3"/>
+      <c r="L60" s="3"/>
       <c r="M60" s="3"/>
     </row>
-    <row r="61" ht="24" customHeight="1" spans="3:13">
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
+    <row r="61" ht="22" customHeight="1" spans="3:13">
+      <c r="C61" s="3">
+        <v>3201</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" s="3">
+        <v>1070</v>
+      </c>
+      <c r="F61" s="3">
+        <v>1175</v>
+      </c>
+      <c r="G61" s="3">
+        <v>3</v>
+      </c>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3"/>
+      <c r="J61" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="K61" s="3">
+        <v>2</v>
+      </c>
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
       <c r="M61" s="3"/>
     </row>
     <row r="62" ht="22" customHeight="1" spans="3:13">
       <c r="C62" s="3">
-        <v>3201</v>
+        <v>3202</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E62" s="3">
         <v>1070</v>
@@ -2956,7 +2955,7 @@
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K62" s="3">
         <v>2</v>
@@ -2968,10 +2967,10 @@
     </row>
     <row r="63" ht="22" customHeight="1" spans="3:13">
       <c r="C63" s="3">
-        <v>3202</v>
+        <v>3203</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E63" s="3">
         <v>1070</v>
@@ -2985,7 +2984,7 @@
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="8" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="K63" s="3">
         <v>2</v>
@@ -2995,75 +2994,59 @@
       </c>
       <c r="M63" s="3"/>
     </row>
-    <row r="64" ht="22" customHeight="1" spans="3:13">
-      <c r="C64" s="3">
-        <v>3203</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E64" s="3">
-        <v>1070</v>
-      </c>
-      <c r="F64" s="3">
-        <v>1175</v>
-      </c>
-      <c r="G64" s="3">
-        <v>3</v>
-      </c>
+    <row r="64" ht="24" customHeight="1" spans="3:13">
+      <c r="C64" s="3"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="3"/>
+      <c r="F64" s="3"/>
+      <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
-      <c r="J64" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="K64" s="3">
+      <c r="J64" s="3"/>
+      <c r="K64" s="3"/>
+      <c r="L64" s="3"/>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" ht="22" customHeight="1" spans="3:13">
+      <c r="C65" s="3">
+        <v>3301</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E65" s="3">
+        <v>1105</v>
+      </c>
+      <c r="F65" s="3">
+        <v>1175</v>
+      </c>
+      <c r="G65" s="3">
         <v>2</v>
       </c>
-      <c r="L64" s="3">
-        <v>0</v>
-      </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" ht="24" customHeight="1" spans="3:13">
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3"/>
+      <c r="J65" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="K65" s="3">
+        <v>0</v>
+      </c>
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
       <c r="M65" s="3"/>
     </row>
-    <row r="66" ht="22" customHeight="1" spans="3:13">
-      <c r="C66" s="3">
-        <v>3301</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E66" s="3">
-        <v>1105</v>
-      </c>
-      <c r="F66" s="3">
-        <v>1175</v>
-      </c>
-      <c r="G66" s="3">
-        <v>2</v>
-      </c>
+    <row r="66" ht="24" customHeight="1" spans="3:13">
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
-      <c r="J66" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="K66" s="3">
-        <v>0</v>
-      </c>
-      <c r="L66" s="3">
-        <v>0</v>
-      </c>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
       <c r="M66" s="3"/>
     </row>
     <row r="67" ht="24" customHeight="1" spans="3:13">
@@ -3287,80 +3270,67 @@
       <c r="L83" s="3"/>
       <c r="M83" s="3"/>
     </row>
-    <row r="84" ht="24" customHeight="1" spans="3:13">
-      <c r="C84" s="3"/>
-      <c r="D84" s="3"/>
-      <c r="E84" s="3"/>
-      <c r="F84" s="3"/>
-      <c r="G84" s="3"/>
-      <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
-      <c r="J84" s="3"/>
-      <c r="K84" s="3"/>
-      <c r="L84" s="3"/>
-      <c r="M84" s="3"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="F36">
+  <conditionalFormatting sqref="F35">
     <cfRule type="duplicateValues" dxfId="0" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F37">
+  <conditionalFormatting sqref="F36">
     <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E38">
+  <conditionalFormatting sqref="E37">
     <cfRule type="duplicateValues" dxfId="0" priority="24"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E39">
+  <conditionalFormatting sqref="E38">
     <cfRule type="duplicateValues" dxfId="0" priority="23"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E40">
+  <conditionalFormatting sqref="E39">
     <cfRule type="duplicateValues" dxfId="0" priority="22"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E41">
+  <conditionalFormatting sqref="E40">
     <cfRule type="duplicateValues" dxfId="0" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E42">
+  <conditionalFormatting sqref="E41">
     <cfRule type="duplicateValues" dxfId="0" priority="11"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E43">
+  <conditionalFormatting sqref="E42">
     <cfRule type="duplicateValues" dxfId="0" priority="10"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E44">
+  <conditionalFormatting sqref="E43">
     <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E45">
+  <conditionalFormatting sqref="E44">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E46">
+  <conditionalFormatting sqref="E45">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F53">
+  <conditionalFormatting sqref="F52">
     <cfRule type="duplicateValues" dxfId="0" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F54">
+  <conditionalFormatting sqref="F53">
     <cfRule type="duplicateValues" dxfId="0" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E55">
+  <conditionalFormatting sqref="E54">
     <cfRule type="duplicateValues" dxfId="0" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E56">
+  <conditionalFormatting sqref="E55">
     <cfRule type="duplicateValues" dxfId="0" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E57">
+  <conditionalFormatting sqref="E56">
     <cfRule type="duplicateValues" dxfId="0" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E58">
+  <conditionalFormatting sqref="E57">
     <cfRule type="duplicateValues" dxfId="0" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E59">
+  <conditionalFormatting sqref="E58">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E60">
+  <conditionalFormatting sqref="E59">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E38:E46 E55:E60 F36:F37 F53:F54" errorStyle="warning">
-      <formula1>COUNTIF($C:$C,E36)&lt;2</formula1>
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E37:E45 E54:E59 F35:F36 F52:F53" errorStyle="warning">
+      <formula1>COUNTIF($C:$C,E35)&lt;2</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:M5" errorStyle="warning">
       <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
